--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14839,10 +14839,10 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P116" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15036,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G116" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15036,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G116" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14839,10 +14839,10 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G116" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14839,10 +14839,10 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G116" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI117"/>
+  <dimension ref="A1:BI119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -945,27 +945,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46136.22916666666</v>
+        <v>46136.27083333334</v>
       </c>
     </row>
     <row r="4">
@@ -1142,27 +1142,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46136.27083333334</v>
+        <v>46136.27430555555</v>
       </c>
     </row>
     <row r="5">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06:35</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46136.27430555555</v>
+        <v>46136.29166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1733,27 +1733,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46136.35416666666</v>
+        <v>46136.33333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46136.375</v>
+        <v>46136.35416666666</v>
       </c>
     </row>
     <row r="10">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46136.41666666666</v>
+        <v>46136.375</v>
       </c>
     </row>
     <row r="11">
@@ -2521,27 +2521,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46136.45833333334</v>
+        <v>46136.375</v>
       </c>
     </row>
     <row r="12">
@@ -2718,27 +2718,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46136.45833333334</v>
+        <v>46136.41666666666</v>
       </c>
     </row>
     <row r="13">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3900,27 +3900,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46136.5</v>
+        <v>46136.45833333334</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46136.51041666666</v>
+        <v>46136.45833333334</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46136.53125</v>
+        <v>46136.5</v>
       </c>
     </row>
     <row r="21">
@@ -4491,27 +4491,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46136.54166666666</v>
+        <v>46136.51041666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46136.54166666666</v>
+        <v>46136.53125</v>
       </c>
     </row>
     <row r="23">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46136.54861111111</v>
+        <v>46136.54166666666</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46136.5625</v>
+        <v>46136.54166666666</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46136.5625</v>
+        <v>46136.54861111111</v>
       </c>
     </row>
     <row r="34">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46136.57291666666</v>
+        <v>46136.5625</v>
       </c>
     </row>
     <row r="36">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46136.58333333334</v>
+        <v>46136.5625</v>
       </c>
     </row>
     <row r="37">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46136.58333333334</v>
+        <v>46136.57291666666</v>
       </c>
     </row>
     <row r="38">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8628,27 +8628,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46136.60416666666</v>
+        <v>46136.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46136.60416666666</v>
+        <v>46136.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46136.625</v>
+        <v>46136.60416666666</v>
       </c>
     </row>
     <row r="56">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46136.625</v>
+        <v>46136.60416666666</v>
       </c>
     </row>
     <row r="57">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14341,12 +14341,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46136.63541666666</v>
+        <v>46136.625</v>
       </c>
     </row>
     <row r="72">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46136.64583333334</v>
+        <v>46136.625</v>
       </c>
     </row>
     <row r="73">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46136.64583333334</v>
+        <v>46136.63541666666</v>
       </c>
     </row>
     <row r="74">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15523,27 +15523,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46136.65625</v>
+        <v>46136.64583333334</v>
       </c>
     </row>
     <row r="78">
@@ -15720,27 +15720,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46136.65625</v>
+        <v>46136.64583333334</v>
       </c>
     </row>
     <row r="79">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17690,27 +17690,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46136.66666666666</v>
+        <v>46136.65625</v>
       </c>
     </row>
     <row r="89">
@@ -17887,12 +17887,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46136.66666666666</v>
+        <v>46136.65625</v>
       </c>
     </row>
     <row r="90">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18675,12 +18675,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,79 +18728,79 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK93" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM93" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN93" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO93" t="n">
         <v>0</v>
@@ -18842,19 +18842,19 @@
         <v>0</v>
       </c>
       <c r="BB93" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC93" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BD93" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE93" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF93" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG93" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46136.72916666666</v>
+        <v>46136.66666666666</v>
       </c>
     </row>
     <row r="94">
@@ -18872,27 +18872,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46136.77083333334</v>
+        <v>46136.66666666666</v>
       </c>
     </row>
     <row r="95">
@@ -19069,27 +19069,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,79 +19122,79 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI95" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK95" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL95" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM95" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN95" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO95" t="n">
         <v>0</v>
@@ -19236,19 +19236,19 @@
         <v>0</v>
       </c>
       <c r="BB95" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC95" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD95" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE95" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF95" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46136.79166666666</v>
+        <v>46136.72916666666</v>
       </c>
     </row>
     <row r="96">
@@ -19266,12 +19266,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46136.83333333334</v>
+        <v>46136.77083333334</v>
       </c>
     </row>
     <row r="97">
@@ -19463,12 +19463,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46136.83333333334</v>
+        <v>46136.79166666666</v>
       </c>
     </row>
     <row r="98">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19857,27 +19857,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46136.875</v>
+        <v>46136.83333333334</v>
       </c>
     </row>
     <row r="100">
@@ -20054,27 +20054,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46136.875</v>
+        <v>46136.83333333334</v>
       </c>
     </row>
     <row r="101">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23403,27 +23403,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23591,6 +23591,400 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
+        <v>46136.875</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Posusje</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI118" s="3" t="n">
+        <v>46136.875</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI119" s="3" t="n">
         <v>46136.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.52</v>
+        <v>3.89</v>
       </c>
       <c r="R47" t="n">
-        <v>4.25</v>
+        <v>5.47</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,17 +9859,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.55</v>
+        <v>3.22</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.89</v>
+        <v>3.17</v>
       </c>
       <c r="R50" t="n">
-        <v>5.47</v>
+        <v>2.22</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G118" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>5.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.71</v>
+        <v>1.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="R74" t="n">
-        <v>2.76</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15036,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G118" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>5.47</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.52</v>
+        <v>3.89</v>
       </c>
       <c r="R56" t="n">
-        <v>4.25</v>
+        <v>5.47</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15036,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G118" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI119"/>
+  <dimension ref="A1:BI115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46136.5</v>
+        <v>46136.47916666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,27 +4491,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46136.51041666666</v>
+        <v>46136.5</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46136.53125</v>
+        <v>46136.51041666666</v>
       </c>
     </row>
     <row r="23">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46136.54166666666</v>
+        <v>46136.53125</v>
       </c>
     </row>
     <row r="24">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6855,27 +6855,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46136.54861111111</v>
+        <v>46136.54166666666</v>
       </c>
     </row>
     <row r="34">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46136.5625</v>
+        <v>46136.54861111111</v>
       </c>
     </row>
     <row r="35">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46136.57291666666</v>
+        <v>46136.5625</v>
       </c>
     </row>
     <row r="38">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46136.58333333334</v>
+        <v>46136.57291666666</v>
       </c>
     </row>
     <row r="39">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9022,27 +9022,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46136.60416666666</v>
+        <v>46136.58333333334</v>
       </c>
     </row>
     <row r="45">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.78</v>
+        <v>3.14</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="R55" t="n">
-        <v>4.25</v>
+        <v>2.18</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="R56" t="n">
-        <v>5.47</v>
+        <v>6.04</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46136.625</v>
+        <v>46136.60416666666</v>
       </c>
     </row>
     <row r="58">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46136.625</v>
+        <v>46136.60416666666</v>
       </c>
     </row>
     <row r="59">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46136.63541666666</v>
+        <v>46136.625</v>
       </c>
     </row>
     <row r="74">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46136.64583333334</v>
+        <v>46136.625</v>
       </c>
     </row>
     <row r="75">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46136.64583333334</v>
+        <v>46136.63541666666</v>
       </c>
     </row>
     <row r="76">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.4</v>
+        <v>2.71</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.33</v>
+        <v>3.23</v>
       </c>
       <c r="R76" t="n">
-        <v>8.699999999999999</v>
+        <v>2.76</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15917,27 +15917,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46136.65625</v>
+        <v>46136.64583333334</v>
       </c>
     </row>
     <row r="80">
@@ -16114,27 +16114,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.14</v>
+        <v>5.33</v>
       </c>
       <c r="R80" t="n">
-        <v>3.59</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46136.65625</v>
+        <v>46136.64583333334</v>
       </c>
     </row>
     <row r="81">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.36</v>
+        <v>2.16</v>
       </c>
       <c r="Q81" t="n">
-        <v>5.11</v>
+        <v>3.18</v>
       </c>
       <c r="R81" t="n">
-        <v>11.7</v>
+        <v>3.11</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="R82" t="n">
-        <v>4.62</v>
+        <v>5.03</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="R85" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="R86" t="n">
-        <v>2.49</v>
+        <v>3.59</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="R87" t="n">
-        <v>3.11</v>
+        <v>2.49</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.48</v>
+        <v>4.6</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="R88" t="n">
-        <v>2.49</v>
+        <v>1.56</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18084,27 +18084,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46136.66666666666</v>
+        <v>46136.65625</v>
       </c>
     </row>
     <row r="91">
@@ -18281,27 +18281,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>3.16</v>
+        <v>1.56</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.16</v>
+        <v>3.8</v>
       </c>
       <c r="R91" t="n">
-        <v>2.3</v>
+        <v>5.41</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46136.66666666666</v>
+        <v>46136.65625</v>
       </c>
     </row>
     <row r="92">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R92" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19069,12 +19069,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,79 +19122,79 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.95</v>
+        <v>2.38</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="R95" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="S95" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI95" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ95" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK95" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM95" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN95" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO95" t="n">
         <v>0</v>
@@ -19236,19 +19236,19 @@
         <v>0</v>
       </c>
       <c r="BB95" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC95" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BD95" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE95" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF95" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46136.72916666666</v>
+        <v>46136.66666666666</v>
       </c>
     </row>
     <row r="96">
@@ -19266,27 +19266,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46136.77083333334</v>
+        <v>46136.66666666666</v>
       </c>
     </row>
     <row r="97">
@@ -19463,27 +19463,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,79 +19516,79 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI97" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK97" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM97" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN97" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO97" t="n">
         <v>0</v>
@@ -19630,19 +19630,19 @@
         <v>0</v>
       </c>
       <c r="BB97" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC97" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD97" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE97" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF97" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG97" t="n">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46136.79166666666</v>
+        <v>46136.72916666666</v>
       </c>
     </row>
     <row r="98">
@@ -19660,12 +19660,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46136.83333333334</v>
+        <v>46136.77083333334</v>
       </c>
     </row>
     <row r="99">
@@ -19857,12 +19857,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46136.83333333334</v>
+        <v>46136.79166666666</v>
       </c>
     </row>
     <row r="100">
@@ -20251,27 +20251,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46136.875</v>
+        <v>46136.83333333334</v>
       </c>
     </row>
     <row r="102">
@@ -20448,27 +20448,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46136.875</v>
+        <v>46136.83333333334</v>
       </c>
     </row>
     <row r="103">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23009,27 +23009,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23197,794 +23197,6 @@
         <v>0</v>
       </c>
       <c r="BI115" s="3" t="n">
-        <v>46136.875</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Washington Spirit</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P116" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R116" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI116" s="3" t="n">
-        <v>46136.875</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Ben Guerdane</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Monastir</t>
-        </is>
-      </c>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" t="n">
-        <v>0</v>
-      </c>
-      <c r="W117" t="n">
-        <v>0</v>
-      </c>
-      <c r="X117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI117" s="3" t="n">
-        <v>46136.875</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Željezničar</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Velež</t>
-        </is>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N118" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI118" s="3" t="n">
-        <v>46136.875</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N119" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" t="n">
-        <v>0</v>
-      </c>
-      <c r="W119" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI119" s="3" t="n">
         <v>46136.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>4.72</v>
+        <v>2.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R50" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.47</v>
+        <v>1.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>3.89</v>
       </c>
       <c r="R51" t="n">
-        <v>2.8</v>
+        <v>5.47</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="R57" t="n">
-        <v>5.47</v>
+        <v>4.72</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11684,7 +11684,7 @@
         <v>1.92</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.71</v>
+        <v>1.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="R76" t="n">
-        <v>2.76</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.14</v>
+        <v>2.71</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="R77" t="n">
-        <v>3.17</v>
+        <v>2.76</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.64</v>
+        <v>2.7</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.22</v>
+        <v>2.95</v>
       </c>
       <c r="R82" t="n">
-        <v>5.03</v>
+        <v>2.49</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.78</v>
+        <v>4.52</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.46</v>
+        <v>4.11</v>
       </c>
       <c r="R83" t="n">
-        <v>4.62</v>
+        <v>1.82</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>4.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.11</v>
+        <v>3.28</v>
       </c>
       <c r="R84" t="n">
-        <v>1.82</v>
+        <v>2.49</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="R85" t="n">
-        <v>2.49</v>
+        <v>5.41</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="R87" t="n">
-        <v>2.49</v>
+        <v>3.59</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>4.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="R88" t="n">
-        <v>1.56</v>
+        <v>5.03</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.11</v>
+        <v>3.46</v>
       </c>
       <c r="R89" t="n">
-        <v>11.7</v>
+        <v>4.62</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,14 +18334,14 @@
         </is>
       </c>
       <c r="P91" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R91" t="n">
         <v>1.56</v>
       </c>
-      <c r="Q91" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R91" t="n">
-        <v>5.41</v>
-      </c>
       <c r="S91" t="n">
         <v>0</v>
       </c>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,55 +18531,55 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="n">
         <v>2.3</v>
       </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="n">
-        <v>0</v>
-      </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.38</v>
+        <v>3.16</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.35</v>
+        <v>3.16</v>
       </c>
       <c r="R95" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="R45" t="n">
-        <v>6.04</v>
+        <v>4.72</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.35</v>
+        <v>1.47</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="R47" t="n">
-        <v>3.04</v>
+        <v>6.04</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>3.89</v>
       </c>
       <c r="R48" t="n">
-        <v>2.6</v>
+        <v>5.47</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.55</v>
+        <v>3.14</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.89</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>5.47</v>
+        <v>2.18</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.78</v>
+        <v>3.22</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="R54" t="n">
-        <v>4.25</v>
+        <v>2.22</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.22</v>
+        <v>2.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="R58" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.33</v>
+        <v>3.4</v>
       </c>
       <c r="R76" t="n">
-        <v>8.699999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="R81" t="n">
-        <v>3.11</v>
+        <v>5.41</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="R82" t="n">
-        <v>2.49</v>
+        <v>3.59</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>4.52</v>
+        <v>1.36</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.11</v>
+        <v>5.11</v>
       </c>
       <c r="R83" t="n">
-        <v>1.82</v>
+        <v>11.7</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.48</v>
+        <v>4.6</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="R84" t="n">
-        <v>2.49</v>
+        <v>1.56</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="R85" t="n">
-        <v>5.41</v>
+        <v>3.11</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="R88" t="n">
-        <v>5.03</v>
+        <v>4.62</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.46</v>
+        <v>2.95</v>
       </c>
       <c r="R89" t="n">
-        <v>4.62</v>
+        <v>2.49</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.11</v>
+        <v>4.22</v>
       </c>
       <c r="R90" t="n">
-        <v>11.7</v>
+        <v>5.03</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="R91" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R92" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,55 +19122,55 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R95" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="n">
         <v>2.3</v>
       </c>
-      <c r="S95" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V95" t="n">
-        <v>0</v>
-      </c>
-      <c r="W95" t="n">
-        <v>0</v>
-      </c>
-      <c r="X95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="n">
-        <v>0</v>
-      </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.38</v>
+        <v>3.16</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.35</v>
+        <v>3.16</v>
       </c>
       <c r="R96" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G114" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.47</v>
+        <v>3.14</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="R47" t="n">
-        <v>6.04</v>
+        <v>2.18</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="R48" t="n">
-        <v>5.47</v>
+        <v>6.04</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R58" t="n">
-        <v>2.6</v>
+        <v>4.25</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.71</v>
+        <v>2.14</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>2.76</v>
+        <v>3.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,14 +16364,14 @@
         </is>
       </c>
       <c r="P81" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R81" t="n">
         <v>1.56</v>
       </c>
-      <c r="Q81" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R81" t="n">
-        <v>5.41</v>
-      </c>
       <c r="S81" t="n">
         <v>0</v>
       </c>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="R82" t="n">
-        <v>3.59</v>
+        <v>2.49</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.11</v>
+        <v>2.95</v>
       </c>
       <c r="R83" t="n">
-        <v>11.7</v>
+        <v>2.49</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>4.6</v>
+        <v>1.36</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.15</v>
+        <v>5.11</v>
       </c>
       <c r="R84" t="n">
-        <v>1.56</v>
+        <v>11.7</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="R85" t="n">
-        <v>3.11</v>
+        <v>5.41</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.52</v>
+        <v>1.78</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.11</v>
+        <v>3.46</v>
       </c>
       <c r="R86" t="n">
-        <v>1.82</v>
+        <v>4.62</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="R89" t="n">
-        <v>2.49</v>
+        <v>3.11</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.48</v>
+        <v>4.52</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.28</v>
+        <v>4.11</v>
       </c>
       <c r="R91" t="n">
-        <v>2.49</v>
+        <v>1.82</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R95" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,55 +19319,55 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="n">
         <v>2.3</v>
       </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="n">
-        <v>0</v>
-      </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G114" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>3.45</v>
+        <v>2.87</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,17 +9268,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.55</v>
+        <v>2.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.89</v>
+        <v>2.75</v>
       </c>
       <c r="R46" t="n">
-        <v>5.47</v>
+        <v>2.7</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="R48" t="n">
-        <v>6.04</v>
+        <v>4.25</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.22</v>
+        <v>2.35</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
-        <v>2.22</v>
+        <v>3.04</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="R58" t="n">
-        <v>4.25</v>
+        <v>4.72</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="R81" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="R82" t="n">
-        <v>2.49</v>
+        <v>3.11</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.56</v>
+        <v>2.13</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="R85" t="n">
-        <v>5.41</v>
+        <v>3.59</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.78</v>
+        <v>4.52</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.46</v>
+        <v>4.11</v>
       </c>
       <c r="R86" t="n">
-        <v>4.62</v>
+        <v>1.82</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.13</v>
+        <v>4.6</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="R87" t="n">
-        <v>3.59</v>
+        <v>1.56</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.18</v>
+        <v>3.46</v>
       </c>
       <c r="R89" t="n">
-        <v>3.11</v>
+        <v>4.62</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>4.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="R91" t="n">
-        <v>1.82</v>
+        <v>5.41</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="R93" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R95" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G114" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>4.3</v>
       </c>
       <c r="Q30" t="n">
         <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.87</v>
+        <v>1.77</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,17 +9268,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="R46" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.78</v>
+        <v>3.22</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="R48" t="n">
-        <v>4.25</v>
+        <v>2.22</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R51" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.1</v>
+        <v>3.89</v>
       </c>
       <c r="R52" t="n">
-        <v>2.6</v>
+        <v>5.47</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="R53" t="n">
-        <v>5.47</v>
+        <v>6.04</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R54" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.65</v>
+        <v>2.47</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="R58" t="n">
-        <v>4.72</v>
+        <v>2.8</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R62" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q79" t="n">
-        <v>5.33</v>
+        <v>3.4</v>
       </c>
       <c r="R79" t="n">
-        <v>8.699999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.71</v>
+        <v>1.4</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="R80" t="n">
-        <v>2.76</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.48</v>
+        <v>4.52</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.28</v>
+        <v>4.11</v>
       </c>
       <c r="R81" t="n">
-        <v>2.49</v>
+        <v>1.82</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.95</v>
+        <v>4.15</v>
       </c>
       <c r="R83" t="n">
-        <v>2.49</v>
+        <v>1.56</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="R85" t="n">
-        <v>3.59</v>
+        <v>2.49</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="R86" t="n">
-        <v>1.82</v>
+        <v>5.41</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="R87" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.64</v>
+        <v>2.13</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.22</v>
+        <v>3.14</v>
       </c>
       <c r="R88" t="n">
-        <v>5.03</v>
+        <v>3.59</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R95" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P114" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R45" t="n">
-        <v>3.04</v>
+        <v>2.18</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
-        <v>4.25</v>
+        <v>3.04</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.65</v>
+        <v>3.22</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.7</v>
+        <v>3.17</v>
       </c>
       <c r="R47" t="n">
-        <v>4.72</v>
+        <v>2.22</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,17 +9859,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.14</v>
+        <v>1.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R49" t="n">
-        <v>2.18</v>
+        <v>4.72</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.55</v>
+        <v>2.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.89</v>
+        <v>2.75</v>
       </c>
       <c r="R52" t="n">
-        <v>5.47</v>
+        <v>2.7</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="R53" t="n">
-        <v>6.04</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.63</v>
+        <v>1.47</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="R54" t="n">
-        <v>2.7</v>
+        <v>6.04</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R58" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R66" t="n">
         <v>2.55</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R66" t="n">
-        <v>2.75</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.4</v>
+        <v>5.33</v>
       </c>
       <c r="R79" t="n">
-        <v>3.17</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.52</v>
+        <v>1.64</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="R81" t="n">
-        <v>1.82</v>
+        <v>5.03</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.18</v>
+        <v>4.15</v>
       </c>
       <c r="R82" t="n">
-        <v>3.11</v>
+        <v>1.56</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.15</v>
+        <v>2.95</v>
       </c>
       <c r="R83" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.7</v>
+        <v>4.52</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.95</v>
+        <v>4.11</v>
       </c>
       <c r="R85" t="n">
-        <v>2.49</v>
+        <v>1.82</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.56</v>
+        <v>2.13</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="R86" t="n">
-        <v>5.41</v>
+        <v>3.59</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="R87" t="n">
-        <v>2.49</v>
+        <v>3.11</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="R88" t="n">
-        <v>3.59</v>
+        <v>2.49</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.46</v>
+        <v>5.11</v>
       </c>
       <c r="R89" t="n">
-        <v>4.62</v>
+        <v>11.7</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="R90" t="n">
-        <v>5.03</v>
+        <v>4.62</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,55 +19319,55 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="n">
         <v>2.3</v>
       </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="n">
-        <v>0</v>
-      </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P114" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI115"/>
+  <dimension ref="A1:BI111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R32" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.14</v>
+        <v>1.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="R45" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.22</v>
+        <v>2.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,17 +9859,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.63</v>
+        <v>3.22</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.75</v>
+        <v>3.17</v>
       </c>
       <c r="R52" t="n">
-        <v>2.7</v>
+        <v>2.22</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.78</v>
+        <v>3.14</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>2.18</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,17 +11041,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.89</v>
+        <v>3.52</v>
       </c>
       <c r="R56" t="n">
-        <v>5.47</v>
+        <v>4.25</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>2.11</v>
+        <v>2.97</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R74" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.71</v>
+        <v>2.14</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>2.76</v>
+        <v>3.17</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.64</v>
+        <v>4.6</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.22</v>
+        <v>4.15</v>
       </c>
       <c r="R81" t="n">
-        <v>5.03</v>
+        <v>1.56</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>4.6</v>
+        <v>4.52</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="R82" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.7</v>
+        <v>1.56</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="R83" t="n">
-        <v>2.49</v>
+        <v>5.41</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>4.52</v>
+        <v>2.7</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.11</v>
+        <v>2.95</v>
       </c>
       <c r="R85" t="n">
-        <v>1.82</v>
+        <v>2.49</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="R86" t="n">
-        <v>3.59</v>
+        <v>2.49</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="R90" t="n">
-        <v>4.62</v>
+        <v>5.03</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.56</v>
+        <v>2.13</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="R91" t="n">
-        <v>5.41</v>
+        <v>3.59</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22221,27 +22221,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22409,794 +22409,6 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46136.875</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Radnik Bijeljina</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Rudar Prijedor</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N112" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI112" s="3" t="n">
-        <v>46136.875</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Club Africain</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Kairouan</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N113" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" t="n">
-        <v>0</v>
-      </c>
-      <c r="V113" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI113" s="3" t="n">
-        <v>46136.875</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>CA Bizertin</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>ES Tunis</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" t="n">
-        <v>0</v>
-      </c>
-      <c r="T114" t="n">
-        <v>0</v>
-      </c>
-      <c r="U114" t="n">
-        <v>0</v>
-      </c>
-      <c r="V114" t="n">
-        <v>0</v>
-      </c>
-      <c r="W114" t="n">
-        <v>0</v>
-      </c>
-      <c r="X114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI114" s="3" t="n">
-        <v>46136.875</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI115" s="3" t="n">
         <v>46136.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>4.3</v>
       </c>
       <c r="Q25" t="n">
         <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>2.87</v>
+        <v>1.77</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="R51" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>1.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="R55" t="n">
-        <v>2.7</v>
+        <v>6.04</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.78</v>
+        <v>3.14</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="R56" t="n">
-        <v>4.25</v>
+        <v>2.18</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.47</v>
+        <v>2.47</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R57" t="n">
-        <v>6.04</v>
+        <v>2.8</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>2.97</v>
+        <v>3.37</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="R72" t="n">
-        <v>3.37</v>
+        <v>2.75</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.71</v>
+        <v>2.14</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="R76" t="n">
-        <v>2.76</v>
+        <v>3.17</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.4</v>
+        <v>2.71</v>
       </c>
       <c r="Q79" t="n">
-        <v>5.33</v>
+        <v>3.23</v>
       </c>
       <c r="R79" t="n">
-        <v>8.699999999999999</v>
+        <v>2.76</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.6</v>
+        <v>1.36</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.15</v>
+        <v>5.11</v>
       </c>
       <c r="R81" t="n">
-        <v>1.56</v>
+        <v>11.7</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>4.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.11</v>
+        <v>3.28</v>
       </c>
       <c r="R82" t="n">
-        <v>1.82</v>
+        <v>2.49</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="R83" t="n">
-        <v>5.41</v>
+        <v>3.11</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.46</v>
+        <v>2.95</v>
       </c>
       <c r="R84" t="n">
-        <v>4.62</v>
+        <v>2.49</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.7</v>
+        <v>4.52</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.95</v>
+        <v>4.11</v>
       </c>
       <c r="R85" t="n">
-        <v>2.49</v>
+        <v>1.82</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.48</v>
+        <v>1.78</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.28</v>
+        <v>3.46</v>
       </c>
       <c r="R86" t="n">
-        <v>2.49</v>
+        <v>4.62</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.16</v>
+        <v>3.06</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="R87" t="n">
-        <v>3.11</v>
+        <v>2.27</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.36</v>
+        <v>4.6</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.11</v>
+        <v>4.15</v>
       </c>
       <c r="R89" t="n">
-        <v>11.7</v>
+        <v>1.56</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="R90" t="n">
-        <v>5.03</v>
+        <v>5.41</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.13</v>
+        <v>1.64</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.14</v>
+        <v>4.22</v>
       </c>
       <c r="R91" t="n">
-        <v>3.59</v>
+        <v>5.03</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R93" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="R94" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R96" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.3</v>
+        <v>1.99</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R25" t="n">
-        <v>1.77</v>
+        <v>3.45</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.55</v>
+        <v>3.14</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.89</v>
+        <v>3.2</v>
       </c>
       <c r="R45" t="n">
-        <v>5.47</v>
+        <v>2.18</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
-        <v>4.72</v>
+        <v>2.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="R50" t="n">
-        <v>4.25</v>
+        <v>6.04</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.47</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="R55" t="n">
-        <v>6.04</v>
+        <v>2.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.47</v>
+        <v>3.22</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="R57" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.22</v>
+        <v>1.65</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.17</v>
+        <v>3.7</v>
       </c>
       <c r="R58" t="n">
-        <v>2.22</v>
+        <v>4.72</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R59" t="n">
-        <v>2.97</v>
+        <v>2.11</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.14</v>
+        <v>2.71</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="R76" t="n">
-        <v>3.17</v>
+        <v>2.76</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.33</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>8.699999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="Q81" t="n">
-        <v>5.11</v>
+        <v>3.8</v>
       </c>
       <c r="R81" t="n">
-        <v>11.7</v>
+        <v>5.41</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.48</v>
+        <v>4.6</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="R82" t="n">
-        <v>2.49</v>
+        <v>1.56</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>4.52</v>
+        <v>1.36</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.11</v>
+        <v>5.11</v>
       </c>
       <c r="R85" t="n">
-        <v>1.82</v>
+        <v>11.7</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="R86" t="n">
-        <v>4.62</v>
+        <v>5.03</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.06</v>
+        <v>2.48</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="R87" t="n">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>4.6</v>
+        <v>3.06</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="R89" t="n">
-        <v>1.56</v>
+        <v>2.27</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.56</v>
+        <v>4.52</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="R90" t="n">
-        <v>5.41</v>
+        <v>1.82</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="R91" t="n">
-        <v>5.03</v>
+        <v>4.62</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R93" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>3.45</v>
+        <v>2.87</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.3</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R31" t="n">
-        <v>1.77</v>
+        <v>3.45</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="R46" t="n">
-        <v>2.6</v>
+        <v>6.04</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>3.89</v>
       </c>
       <c r="R47" t="n">
-        <v>3.04</v>
+        <v>5.47</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.47</v>
+        <v>3.22</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.1</v>
+        <v>3.17</v>
       </c>
       <c r="R50" t="n">
-        <v>6.04</v>
+        <v>2.22</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="R52" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.89</v>
+        <v>3.52</v>
       </c>
       <c r="R54" t="n">
-        <v>5.47</v>
+        <v>4.25</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="R57" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.65</v>
+        <v>2.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="R58" t="n">
-        <v>4.72</v>
+        <v>2.7</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.56</v>
+        <v>4.52</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="R81" t="n">
-        <v>5.41</v>
+        <v>1.82</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.18</v>
+        <v>3.46</v>
       </c>
       <c r="R83" t="n">
-        <v>3.11</v>
+        <v>4.62</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.7</v>
+        <v>1.56</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="R84" t="n">
-        <v>2.49</v>
+        <v>5.41</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.11</v>
+        <v>4.22</v>
       </c>
       <c r="R85" t="n">
-        <v>11.7</v>
+        <v>5.03</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.64</v>
+        <v>2.48</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.22</v>
+        <v>3.28</v>
       </c>
       <c r="R86" t="n">
-        <v>5.03</v>
+        <v>2.49</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="R87" t="n">
-        <v>2.49</v>
+        <v>3.59</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="R88" t="n">
-        <v>3.59</v>
+        <v>3.11</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="R89" t="n">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>4.52</v>
+        <v>3.06</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.11</v>
+        <v>3.34</v>
       </c>
       <c r="R90" t="n">
-        <v>1.82</v>
+        <v>2.27</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.46</v>
+        <v>5.11</v>
       </c>
       <c r="R91" t="n">
-        <v>4.62</v>
+        <v>11.7</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="R93" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.47</v>
+        <v>2.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="R46" t="n">
-        <v>6.04</v>
+        <v>2.7</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.89</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>5.47</v>
+        <v>3.04</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,17 +9859,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.47</v>
+        <v>3.22</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="R49" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="R54" t="n">
-        <v>4.25</v>
+        <v>4.72</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.14</v>
+        <v>1.47</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="R57" t="n">
-        <v>2.18</v>
+        <v>6.04</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R58" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R67" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>2.11</v>
+        <v>2.97</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.14</v>
+        <v>2.71</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="R78" t="n">
-        <v>3.17</v>
+        <v>2.76</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>4.6</v>
+        <v>1.78</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.15</v>
+        <v>3.46</v>
       </c>
       <c r="R82" t="n">
-        <v>1.56</v>
+        <v>4.62</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.46</v>
+        <v>3.14</v>
       </c>
       <c r="R83" t="n">
-        <v>4.62</v>
+        <v>3.59</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.56</v>
+        <v>3.06</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="R84" t="n">
-        <v>5.41</v>
+        <v>2.27</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.64</v>
+        <v>2.16</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.22</v>
+        <v>3.18</v>
       </c>
       <c r="R85" t="n">
-        <v>5.03</v>
+        <v>3.11</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="R86" t="n">
-        <v>2.49</v>
+        <v>5.41</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.13</v>
+        <v>4.6</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="R87" t="n">
-        <v>3.59</v>
+        <v>1.56</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.18</v>
+        <v>4.22</v>
       </c>
       <c r="R88" t="n">
-        <v>3.11</v>
+        <v>5.03</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>3.06</v>
+        <v>2.48</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="R90" t="n">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R93" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="R94" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R96" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.3</v>
+        <v>1.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.77</v>
+        <v>3.39</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R32" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="R45" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="R46" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,17 +9662,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,17 +9859,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.14</v>
+        <v>1.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="R52" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.55</v>
+        <v>3.22</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.89</v>
+        <v>3.17</v>
       </c>
       <c r="R53" t="n">
-        <v>5.47</v>
+        <v>2.22</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="R55" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.47</v>
+        <v>2.92</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
       <c r="R57" t="n">
-        <v>6.04</v>
+        <v>2.26</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R58" t="n">
-        <v>2.6</v>
+        <v>4.72</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>5.33</v>
       </c>
       <c r="R77" t="n">
-        <v>3.17</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.4</v>
+        <v>2.71</v>
       </c>
       <c r="Q79" t="n">
-        <v>5.33</v>
+        <v>3.23</v>
       </c>
       <c r="R79" t="n">
-        <v>8.699999999999999</v>
+        <v>2.76</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="R81" t="n">
-        <v>1.82</v>
+        <v>5.41</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,55 +16561,55 @@
         </is>
       </c>
       <c r="P82" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q82" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R82" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>0</v>
-      </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.06</v>
+        <v>1.64</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.34</v>
+        <v>4.22</v>
       </c>
       <c r="R84" t="n">
-        <v>2.27</v>
+        <v>5.03</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.18</v>
+        <v>3.46</v>
       </c>
       <c r="R85" t="n">
-        <v>3.11</v>
+        <v>4.62</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.56</v>
+        <v>2.48</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="R86" t="n">
-        <v>5.41</v>
+        <v>2.49</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>4.6</v>
+        <v>4.52</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="R87" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.64</v>
+        <v>2.16</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.22</v>
+        <v>3.18</v>
       </c>
       <c r="R88" t="n">
-        <v>5.03</v>
+        <v>3.11</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="R89" t="n">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.48</v>
+        <v>1.36</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.28</v>
+        <v>5.11</v>
       </c>
       <c r="R90" t="n">
-        <v>2.49</v>
+        <v>11.7</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.11</v>
+        <v>2.95</v>
       </c>
       <c r="R91" t="n">
-        <v>11.7</v>
+        <v>2.49</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.91</v>
+        <v>3.16</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="R95" t="n">
-        <v>3.97</v>
+        <v>2.3</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P109" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
         <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="R46" t="n">
-        <v>4.25</v>
+        <v>4.72</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,17 +9662,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>2.18</v>
+        <v>3.04</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.47</v>
+        <v>3.22</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.1</v>
+        <v>3.17</v>
       </c>
       <c r="R50" t="n">
-        <v>6.04</v>
+        <v>2.22</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.55</v>
+        <v>3.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.89</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>5.47</v>
+        <v>2.18</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>1.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="R55" t="n">
-        <v>2.7</v>
+        <v>6.04</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.6</v>
+        <v>2.92</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>2.26</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="R57" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R69" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="R73" t="n">
-        <v>2.11</v>
+        <v>3.37</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.09</v>
+        <v>2.65</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R74" t="n">
-        <v>3.37</v>
+        <v>2.55</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.71</v>
+        <v>3.17</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="R79" t="n">
-        <v>2.76</v>
+        <v>2.21</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,14 +16364,14 @@
         </is>
       </c>
       <c r="P81" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R81" t="n">
         <v>1.56</v>
       </c>
-      <c r="Q81" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R81" t="n">
-        <v>5.41</v>
-      </c>
       <c r="S81" t="n">
         <v>0</v>
       </c>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>4.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="R82" t="n">
-        <v>1.56</v>
+        <v>5.03</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.13</v>
+        <v>1.36</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.14</v>
+        <v>5.11</v>
       </c>
       <c r="R83" t="n">
-        <v>3.59</v>
+        <v>11.7</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.64</v>
+        <v>3.06</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.22</v>
+        <v>3.34</v>
       </c>
       <c r="R84" t="n">
-        <v>5.03</v>
+        <v>2.27</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.46</v>
+        <v>3.14</v>
       </c>
       <c r="R85" t="n">
-        <v>4.62</v>
+        <v>3.59</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.48</v>
+        <v>4.52</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.28</v>
+        <v>4.11</v>
       </c>
       <c r="R86" t="n">
-        <v>2.49</v>
+        <v>1.82</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>4.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="R87" t="n">
-        <v>1.82</v>
+        <v>5.41</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="R88" t="n">
-        <v>3.11</v>
+        <v>2.49</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="R89" t="n">
-        <v>2.27</v>
+        <v>3.11</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.36</v>
+        <v>2.48</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.11</v>
+        <v>3.28</v>
       </c>
       <c r="R90" t="n">
-        <v>11.7</v>
+        <v>2.49</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.95</v>
+        <v>3.46</v>
       </c>
       <c r="R91" t="n">
-        <v>2.49</v>
+        <v>4.62</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.91</v>
+        <v>3.16</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="R92" t="n">
-        <v>3.97</v>
+        <v>2.3</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R94" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>3.16</v>
+        <v>1.91</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="R95" t="n">
-        <v>2.3</v>
+        <v>3.97</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>3.39</v>
+        <v>2.87</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="R45" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.52</v>
+        <v>3.18</v>
       </c>
       <c r="R47" t="n">
-        <v>4.25</v>
+        <v>2.26</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R48" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R49" t="n">
-        <v>3.04</v>
+        <v>4.72</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.47</v>
+        <v>1.47</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R51" t="n">
-        <v>2.8</v>
+        <v>6.04</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>2.18</v>
+        <v>3.04</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.47</v>
+        <v>2.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R55" t="n">
-        <v>6.04</v>
+        <v>2.8</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="R57" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.14</v>
+        <v>2.71</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="R76" t="n">
-        <v>3.17</v>
+        <v>2.76</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.71</v>
+        <v>3.17</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="R78" t="n">
-        <v>2.76</v>
+        <v>2.21</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.6</v>
+        <v>1.78</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.15</v>
+        <v>3.46</v>
       </c>
       <c r="R81" t="n">
-        <v>1.56</v>
+        <v>4.62</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="R82" t="n">
-        <v>5.03</v>
+        <v>5.41</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="R84" t="n">
-        <v>2.27</v>
+        <v>1.56</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.13</v>
+        <v>4.52</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.14</v>
+        <v>4.11</v>
       </c>
       <c r="R85" t="n">
-        <v>3.59</v>
+        <v>1.82</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.52</v>
+        <v>1.64</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="R86" t="n">
-        <v>1.82</v>
+        <v>5.03</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.56</v>
+        <v>3.06</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="R87" t="n">
-        <v>5.41</v>
+        <v>2.27</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,10 +17743,10 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="R88" t="n">
         <v>2.49</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,10 +18137,10 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="R90" t="n">
         <v>2.49</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.46</v>
+        <v>3.14</v>
       </c>
       <c r="R91" t="n">
-        <v>4.62</v>
+        <v>3.59</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.16</v>
+        <v>1.91</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="R92" t="n">
-        <v>2.3</v>
+        <v>3.97</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R94" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="R95" t="n">
-        <v>3.97</v>
+        <v>2.75</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P109" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R31" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>3.39</v>
+        <v>2.87</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="R36" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.63</v>
+        <v>3.22</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.75</v>
+        <v>3.17</v>
       </c>
       <c r="R45" t="n">
-        <v>2.7</v>
+        <v>2.22</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.14</v>
+        <v>1.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="R48" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.22</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="R50" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.47</v>
+        <v>2.92</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
       <c r="R51" t="n">
-        <v>6.04</v>
+        <v>2.26</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="R52" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="R54" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.47</v>
+        <v>1.65</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="R55" t="n">
-        <v>2.8</v>
+        <v>4.72</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R56" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="R57" t="n">
-        <v>4.25</v>
+        <v>6.04</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="R58" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="R60" t="n">
-        <v>3.37</v>
+        <v>2.11</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="R67" t="n">
-        <v>2.11</v>
+        <v>3.37</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.71</v>
+        <v>3.17</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="R76" t="n">
-        <v>2.76</v>
+        <v>2.21</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.4</v>
+        <v>2.71</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.33</v>
+        <v>3.23</v>
       </c>
       <c r="R77" t="n">
-        <v>8.699999999999999</v>
+        <v>2.76</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.17</v>
+        <v>1.4</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.28</v>
+        <v>5.33</v>
       </c>
       <c r="R78" t="n">
-        <v>2.21</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15824,10 +15824,10 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="R80" t="n">
-        <v>3.17</v>
+        <v>5.7</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.46</v>
+        <v>3.14</v>
       </c>
       <c r="R81" t="n">
-        <v>4.62</v>
+        <v>3.59</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.8</v>
+        <v>5.11</v>
       </c>
       <c r="R82" t="n">
-        <v>5.41</v>
+        <v>11.7</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.36</v>
+        <v>3.06</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.11</v>
+        <v>3.34</v>
       </c>
       <c r="R83" t="n">
-        <v>11.7</v>
+        <v>2.27</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>4.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="R84" t="n">
-        <v>1.56</v>
+        <v>5.03</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.64</v>
+        <v>2.48</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.22</v>
+        <v>3.28</v>
       </c>
       <c r="R86" t="n">
-        <v>5.03</v>
+        <v>2.49</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="R87" t="n">
-        <v>2.27</v>
+        <v>1.56</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,10 +17743,10 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="R88" t="n">
         <v>2.49</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="R89" t="n">
-        <v>3.11</v>
+        <v>5.41</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="R90" t="n">
-        <v>2.49</v>
+        <v>3.11</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.14</v>
+        <v>3.46</v>
       </c>
       <c r="R91" t="n">
-        <v>3.59</v>
+        <v>4.62</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="R92" t="n">
-        <v>3.97</v>
+        <v>2.75</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,55 +18925,55 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R94" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="n">
         <v>2.3</v>
       </c>
-      <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" t="n">
-        <v>0</v>
-      </c>
-      <c r="V94" t="n">
-        <v>0</v>
-      </c>
-      <c r="W94" t="n">
-        <v>0</v>
-      </c>
-      <c r="X94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="n">
-        <v>0</v>
-      </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R96" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,17 +9268,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.36</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R50" t="n">
-        <v>2.6</v>
+        <v>4.72</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.78</v>
+        <v>3.22</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>2.22</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="R55" t="n">
-        <v>4.72</v>
+        <v>6.04</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R56" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.47</v>
+        <v>2.92</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
       <c r="R57" t="n">
-        <v>6.04</v>
+        <v>2.26</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="R58" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R62" t="n">
-        <v>2.75</v>
+        <v>3.37</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R63" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.71</v>
+        <v>1.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="R77" t="n">
-        <v>2.76</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.4</v>
+        <v>2.71</v>
       </c>
       <c r="Q78" t="n">
-        <v>5.33</v>
+        <v>3.23</v>
       </c>
       <c r="R78" t="n">
-        <v>8.699999999999999</v>
+        <v>2.76</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15824,10 +15824,10 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="R79" t="n">
-        <v>3.17</v>
+        <v>5.7</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="R80" t="n">
-        <v>5.7</v>
+        <v>3.17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.13</v>
+        <v>1.36</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.14</v>
+        <v>5.11</v>
       </c>
       <c r="R81" t="n">
-        <v>3.59</v>
+        <v>11.7</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.36</v>
+        <v>4.6</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.11</v>
+        <v>4.15</v>
       </c>
       <c r="R82" t="n">
-        <v>11.7</v>
+        <v>1.56</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="R83" t="n">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.64</v>
+        <v>3.06</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.22</v>
+        <v>3.34</v>
       </c>
       <c r="R84" t="n">
-        <v>5.03</v>
+        <v>2.27</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>4.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.11</v>
+        <v>3.28</v>
       </c>
       <c r="R85" t="n">
-        <v>1.82</v>
+        <v>2.49</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.48</v>
+        <v>4.52</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.28</v>
+        <v>4.11</v>
       </c>
       <c r="R86" t="n">
-        <v>2.49</v>
+        <v>1.82</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>4.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.15</v>
+        <v>3.14</v>
       </c>
       <c r="R87" t="n">
-        <v>1.56</v>
+        <v>3.59</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.7</v>
+        <v>1.56</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="R88" t="n">
-        <v>2.49</v>
+        <v>5.41</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.8</v>
+        <v>4.22</v>
       </c>
       <c r="R89" t="n">
-        <v>5.41</v>
+        <v>5.03</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20891,17 +20891,17 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G110" t="n">

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI111"/>
+  <dimension ref="A1:BI112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R32" t="n">
-        <v>2.87</v>
+        <v>3.39</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.44</v>
+        <v>1.96</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="R43" t="n">
-        <v>2.3</v>
+        <v>4.25</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.55</v>
+        <v>2.92</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R46" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.89</v>
+        <v>3</v>
       </c>
       <c r="R48" t="n">
-        <v>5.47</v>
+        <v>3.04</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="R49" t="n">
-        <v>7.36</v>
+        <v>5.47</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="R50" t="n">
-        <v>4.72</v>
+        <v>7.36</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="R51" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.22</v>
+        <v>1.78</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.17</v>
+        <v>3.52</v>
       </c>
       <c r="R53" t="n">
-        <v>2.22</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="R54" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="R55" t="n">
-        <v>6.04</v>
+        <v>4.72</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.63</v>
+        <v>1.47</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="R56" t="n">
-        <v>2.7</v>
+        <v>6.04</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.92</v>
+        <v>2.47</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="R57" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.78</v>
+        <v>3.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="R58" t="n">
-        <v>4.25</v>
+        <v>2.18</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.05</v>
+        <v>3.99</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R61" t="n">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.99</v>
+        <v>3.05</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R72" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.36</v>
+        <v>2.13</v>
       </c>
       <c r="Q81" t="n">
-        <v>5.11</v>
+        <v>3.14</v>
       </c>
       <c r="R81" t="n">
-        <v>11.7</v>
+        <v>3.59</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.15</v>
+        <v>2.95</v>
       </c>
       <c r="R82" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,10 +16758,10 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="R83" t="n">
         <v>2.49</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="R85" t="n">
-        <v>2.49</v>
+        <v>3.11</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.52</v>
+        <v>1.64</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="R86" t="n">
-        <v>1.82</v>
+        <v>5.03</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.13</v>
+        <v>4.52</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.14</v>
+        <v>4.11</v>
       </c>
       <c r="R87" t="n">
-        <v>3.59</v>
+        <v>1.82</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.8</v>
+        <v>5.11</v>
       </c>
       <c r="R88" t="n">
-        <v>5.41</v>
+        <v>11.7</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="R89" t="n">
-        <v>5.03</v>
+        <v>5.41</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.18</v>
+        <v>4.15</v>
       </c>
       <c r="R90" t="n">
-        <v>3.11</v>
+        <v>1.56</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="R96" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19463,12 +19463,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,79 +19516,79 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R97" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="S97" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI97" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ97" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK97" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL97" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM97" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN97" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO97" t="n">
         <v>0</v>
@@ -19630,19 +19630,19 @@
         <v>0</v>
       </c>
       <c r="BB97" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC97" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BD97" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE97" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF97" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG97" t="n">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46136.72916666666</v>
+        <v>46136.67708333334</v>
       </c>
     </row>
     <row r="98">
@@ -19660,27 +19660,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,79 +19713,79 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="R98" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI98" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK98" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL98" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN98" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO98" t="n">
         <v>0</v>
@@ -19827,19 +19827,19 @@
         <v>0</v>
       </c>
       <c r="BB98" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC98" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD98" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE98" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF98" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46136.77083333334</v>
+        <v>46136.72916666666</v>
       </c>
     </row>
     <row r="99">
@@ -19857,12 +19857,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46136.79166666666</v>
+        <v>46136.77083333334</v>
       </c>
     </row>
     <row r="100">
@@ -20054,12 +20054,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46136.83333333334</v>
+        <v>46136.79166666666</v>
       </c>
     </row>
     <row r="101">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20645,12 +20645,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46136.875</v>
+        <v>46136.83333333334</v>
       </c>
     </row>
     <row r="104">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22409,6 +22409,203 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
+        <v>46136.875</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI112" s="3" t="n">
         <v>46136.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>2.87</v>
+        <v>3.39</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,17 +9268,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
-        <v>2.26</v>
+        <v>3.04</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R47" t="n">
-        <v>2.6</v>
+        <v>4.25</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>3.89</v>
       </c>
       <c r="R48" t="n">
-        <v>3.04</v>
+        <v>5.47</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="R49" t="n">
-        <v>5.47</v>
+        <v>6.04</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.46</v>
+        <v>2.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="R50" t="n">
-        <v>7.36</v>
+        <v>2.7</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.22</v>
+        <v>2.47</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.6</v>
+        <v>3.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>5</v>
+        <v>2.18</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R54" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.65</v>
+        <v>2.92</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="R55" t="n">
-        <v>4.72</v>
+        <v>2.26</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="R56" t="n">
-        <v>6.04</v>
+        <v>4.72</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="R57" t="n">
-        <v>2.8</v>
+        <v>7.36</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="R58" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.99</v>
+        <v>2.55</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R61" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R62" t="n">
-        <v>2.97</v>
+        <v>2.11</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>2.11</v>
+        <v>2.97</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.65</v>
+        <v>2.09</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="R74" t="n">
-        <v>2.55</v>
+        <v>3.37</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R76" t="n">
         <v>3.17</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R76" t="n">
-        <v>2.21</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.4</v>
+        <v>2.71</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.33</v>
+        <v>3.23</v>
       </c>
       <c r="R77" t="n">
-        <v>8.699999999999999</v>
+        <v>2.76</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.71</v>
+        <v>1.4</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="R78" t="n">
-        <v>2.76</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15824,10 +15824,10 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.14</v>
+        <v>3.17</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="R80" t="n">
-        <v>3.17</v>
+        <v>2.21</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.13</v>
+        <v>4.52</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.14</v>
+        <v>4.11</v>
       </c>
       <c r="R81" t="n">
-        <v>3.59</v>
+        <v>1.82</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.7</v>
+        <v>1.36</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.95</v>
+        <v>5.11</v>
       </c>
       <c r="R82" t="n">
-        <v>2.49</v>
+        <v>11.7</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="R83" t="n">
-        <v>2.49</v>
+        <v>5.41</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.06</v>
+        <v>1.64</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.34</v>
+        <v>4.22</v>
       </c>
       <c r="R84" t="n">
-        <v>2.27</v>
+        <v>5.03</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="R85" t="n">
-        <v>3.11</v>
+        <v>3.59</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="R86" t="n">
-        <v>5.03</v>
+        <v>4.62</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>4.52</v>
+        <v>2.7</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.11</v>
+        <v>2.95</v>
       </c>
       <c r="R87" t="n">
-        <v>1.82</v>
+        <v>2.49</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.36</v>
+        <v>2.16</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.11</v>
+        <v>3.18</v>
       </c>
       <c r="R88" t="n">
-        <v>11.7</v>
+        <v>3.11</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.56</v>
+        <v>3.06</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="R89" t="n">
-        <v>5.41</v>
+        <v>2.27</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="R90" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,55 +18334,55 @@
         </is>
       </c>
       <c r="P91" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q91" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R91" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" t="n">
-        <v>0</v>
-      </c>
-      <c r="X91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>0</v>
-      </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.91</v>
+        <v>3.16</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="R93" t="n">
-        <v>3.97</v>
+        <v>2.3</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="R94" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="R96" t="n">
-        <v>2.75</v>
+        <v>3.97</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20891,17 +20891,17 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI112"/>
+  <dimension ref="A1:BI113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.3</v>
+        <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.77</v>
+        <v>3.39</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>4.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>3.45</v>
+        <v>1.77</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R33" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46136.57291666666</v>
+        <v>46136.5625</v>
       </c>
     </row>
     <row r="39">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46136.58333333334</v>
+        <v>46136.57291666666</v>
       </c>
     </row>
     <row r="40">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>3.44</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="R45" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46136.60416666666</v>
+        <v>46136.58333333334</v>
       </c>
     </row>
     <row r="46">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,17 +9465,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.78</v>
+        <v>3.22</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="R47" t="n">
-        <v>4.25</v>
+        <v>2.22</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="R48" t="n">
-        <v>5.47</v>
+        <v>7.36</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="R49" t="n">
-        <v>6.04</v>
+        <v>4.25</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.63</v>
+        <v>1.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="R50" t="n">
-        <v>2.7</v>
+        <v>6.04</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.47</v>
+        <v>3.14</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.14</v>
+        <v>1.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="R52" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R54" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.92</v>
+        <v>1.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>2.26</v>
+        <v>5</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.65</v>
+        <v>2.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="R56" t="n">
-        <v>4.72</v>
+        <v>2.7</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="R57" t="n">
-        <v>7.36</v>
+        <v>4.72</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.22</v>
+        <v>2.92</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="R58" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.99</v>
+        <v>2.47</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="R59" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46136.625</v>
+        <v>46136.60416666666</v>
       </c>
     </row>
     <row r="60">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R66" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.09</v>
+        <v>2.65</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R74" t="n">
-        <v>3.37</v>
+        <v>2.55</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>4.21</v>
+        <v>3.05</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R75" t="n">
-        <v>1.64</v>
+        <v>2.11</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46136.63541666666</v>
+        <v>46136.625</v>
       </c>
     </row>
     <row r="76">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.14</v>
+        <v>4.21</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>3.17</v>
+        <v>1.64</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46136.64583333334</v>
+        <v>46136.63541666666</v>
       </c>
     </row>
     <row r="77">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.71</v>
+        <v>1.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="R77" t="n">
-        <v>2.76</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q78" t="n">
-        <v>5.33</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>8.699999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15824,10 +15824,10 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -16311,12 +16311,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.52</v>
+        <v>2.71</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.11</v>
+        <v>3.23</v>
       </c>
       <c r="R81" t="n">
-        <v>1.82</v>
+        <v>2.76</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>46136.65625</v>
+        <v>46136.64583333334</v>
       </c>
     </row>
     <row r="82">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.36</v>
+        <v>2.48</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.11</v>
+        <v>3.28</v>
       </c>
       <c r="R82" t="n">
-        <v>11.7</v>
+        <v>2.49</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.56</v>
+        <v>3.06</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="R83" t="n">
-        <v>5.41</v>
+        <v>2.27</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.64</v>
+        <v>2.13</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.22</v>
+        <v>3.14</v>
       </c>
       <c r="R84" t="n">
-        <v>5.03</v>
+        <v>3.59</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.14</v>
+        <v>3.46</v>
       </c>
       <c r="R85" t="n">
-        <v>3.59</v>
+        <v>4.62</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.46</v>
+        <v>5.11</v>
       </c>
       <c r="R86" t="n">
-        <v>4.62</v>
+        <v>11.7</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.7</v>
+        <v>4.52</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.95</v>
+        <v>4.11</v>
       </c>
       <c r="R87" t="n">
-        <v>2.49</v>
+        <v>1.82</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="R88" t="n">
-        <v>3.11</v>
+        <v>5.41</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="R89" t="n">
-        <v>2.27</v>
+        <v>3.11</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,10 +18137,10 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="R90" t="n">
         <v>2.49</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>4.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="R91" t="n">
-        <v>1.56</v>
+        <v>5.03</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18478,27 +18478,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.98</v>
+        <v>4.6</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="R92" t="n">
-        <v>2.65</v>
+        <v>1.56</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46136.66666666666</v>
+        <v>46136.65625</v>
       </c>
     </row>
     <row r="93">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.16</v>
+        <v>1.91</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="R93" t="n">
-        <v>2.3</v>
+        <v>3.97</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.91</v>
+        <v>3.16</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="R96" t="n">
-        <v>3.97</v>
+        <v>2.3</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19463,12 +19463,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.25</v>
+        <v>2.98</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R97" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46136.67708333334</v>
+        <v>46136.66666666666</v>
       </c>
     </row>
     <row r="98">
@@ -19660,12 +19660,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,79 +19713,79 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R98" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="S98" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI98" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ98" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK98" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL98" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM98" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN98" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO98" t="n">
         <v>0</v>
@@ -19827,19 +19827,19 @@
         <v>0</v>
       </c>
       <c r="BB98" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC98" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BD98" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE98" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF98" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46136.72916666666</v>
+        <v>46136.67708333334</v>
       </c>
     </row>
     <row r="99">
@@ -19857,27 +19857,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,79 +19910,79 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="R99" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI99" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK99" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN99" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO99" t="n">
         <v>0</v>
@@ -20024,19 +20024,19 @@
         <v>0</v>
       </c>
       <c r="BB99" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC99" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE99" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF99" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG99" t="n">
         <v>0</v>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46136.77083333334</v>
+        <v>46136.72916666666</v>
       </c>
     </row>
     <row r="100">
@@ -20054,12 +20054,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46136.79166666666</v>
+        <v>46136.77083333334</v>
       </c>
     </row>
     <row r="101">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46136.83333333334</v>
+        <v>46136.79166666666</v>
       </c>
     </row>
     <row r="102">
@@ -20842,12 +20842,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46136.875</v>
+        <v>46136.83333333334</v>
       </c>
     </row>
     <row r="105">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22418,12 +22418,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22606,6 +22606,203 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
+        <v>46136.875</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI113" s="3" t="n">
         <v>46136.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-24.xlsx
+++ b/jogos_2026-04-24.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>4.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>3.39</v>
+        <v>1.77</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.02</v>
+        <v>2.37</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.74</v>
+        <v>3.44</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.68</v>
+        <v>2.67</v>
       </c>
       <c r="R43" t="n">
-        <v>4.52</v>
+        <v>2.3</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.44</v>
+        <v>1.74</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.67</v>
+        <v>3.68</v>
       </c>
       <c r="R45" t="n">
-        <v>2.3</v>
+        <v>4.52</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,17 +9465,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>7.36</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.22</v>
+        <v>1.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="R47" t="n">
-        <v>2.22</v>
+        <v>5</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.95</v>
+        <v>3.52</v>
       </c>
       <c r="R48" t="n">
-        <v>7.36</v>
+        <v>4.25</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.78</v>
+        <v>3.22</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="R49" t="n">
-        <v>4.25</v>
+        <v>2.22</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R51" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="R52" t="n">
-        <v>5.47</v>
+        <v>4.72</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10699,7 +10699,7 @@
         <v>1.92</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R54" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R55" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="R56" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.7</v>
+        <v>3.89</v>
       </c>
       <c r="R57" t="n">
-        <v>4.72</v>
+        <v>5.47</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11684,7 +11684,7 @@
         <v>1.92</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.92</v>
+        <v>1.47</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.18</v>
+        <v>4.1</v>
       </c>
       <c r="R58" t="n">
-        <v>2.26</v>
+        <v>6.04</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.99</v>
+        <v>3.05</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R73" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.4</v>
+        <v>3.17</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.33</v>
+        <v>3.28</v>
       </c>
       <c r="R77" t="n">
-        <v>8.699999999999999</v>
+        <v>2.21</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="R80" t="n">
-        <v>2.21</v>
+        <v>2.76</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.71</v>
+        <v>1.4</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="R81" t="n">
-        <v>2.76</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16415,10 +16415,10 @@
         <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.48</v>
+        <v>1.36</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.28</v>
+        <v>5.11</v>
       </c>
       <c r="R82" t="n">
-        <v>2.49</v>
+        <v>11.7</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.06</v>
+        <v>2.13</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="R83" t="n">
-        <v>2.27</v>
+        <v>3.59</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="R84" t="n">
-        <v>3.59</v>
+        <v>2.49</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.78</v>
+        <v>4.52</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.46</v>
+        <v>4.11</v>
       </c>
       <c r="R85" t="n">
-        <v>4.62</v>
+        <v>1.82</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.11</v>
+        <v>3.46</v>
       </c>
       <c r="R86" t="n">
-        <v>11.7</v>
+        <v>4.62</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>4.52</v>
+        <v>4.6</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.11</v>
+        <v>4.15</v>
       </c>
       <c r="R87" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.56</v>
+        <v>3.06</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="R88" t="n">
-        <v>5.41</v>
+        <v>2.27</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.95</v>
+        <v>4.22</v>
       </c>
       <c r="R90" t="n">
-        <v>2.49</v>
+        <v>5.03</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="R91" t="n">
-        <v>5.03</v>
+        <v>5.41</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.15</v>
+        <v>2.95</v>
       </c>
       <c r="R92" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="R93" t="n">
-        <v>3.97</v>
+        <v>2.75</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R95" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="R97" t="n">
-        <v>2.65</v>
+        <v>3.97</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G111" t="n">
